--- a/packages/calculators/src/modules/test/5.3-lime.xlsx
+++ b/packages/calculators/src/modules/test/5.3-lime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7237D5-2FD2-9848-902D-C7DDEE7B4271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBC98C2-61D3-874A-BBFD-71C428AB48F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="19580" windowWidth="28800" windowHeight="23520" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="5.3.1.1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Method 1</t>
   </si>
@@ -47,146 +47,6 @@
     <t>Constants</t>
   </si>
   <si>
-    <r>
-      <t>𝐸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">𝑙𝑖𝑚𝑒 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>= [(𝑀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">𝑙𝑖𝑚𝑒 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>× 𝐹𝑟𝑎𝑐𝐿𝑖𝑚𝑒 × 𝑃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">𝑙𝑖𝑚𝑒 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">× 𝐸𝐹 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>𝑙𝑖𝑚𝑒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>) + (𝑀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">𝑙𝑖𝑚𝑒 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>× 𝐹𝑟𝑎𝑐𝐷𝑜𝑙 × 𝑃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">𝑑𝑜𝑙 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">× 𝐸𝐹 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>𝑑𝑜𝑙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>)] × 𝐶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>𝐶𝑂2</t>
-    </r>
-  </si>
-  <si>
     <t>Elime</t>
   </si>
   <si>
@@ -202,12 +62,6 @@
     <t>Fraction of lime as limestone</t>
   </si>
   <si>
-    <t>FracDol</t>
-  </si>
-  <si>
-    <t>Fraction of lime as dolomite</t>
-  </si>
-  <si>
     <t>Plime</t>
   </si>
   <si>
@@ -218,13 +72,31 @@
   </si>
   <si>
     <t>Efdol</t>
+  </si>
+  <si>
+    <t>𝐸𝑙𝑖𝑚𝑒 = [(𝑀𝑙𝑖𝑚𝑒 × 𝐹𝑟𝑎𝑐𝐿𝑖𝑚𝑒 × 𝑃𝑙𝑖𝑚𝑒 × 𝐸𝐹 𝑙𝑖𝑚𝑒) + (𝑀𝑙𝑖𝑚𝑒 × (1 − 𝐹𝑟𝑎𝑐𝐿𝑖𝑚𝑒) × 𝑃𝑑𝑜𝑙 × 𝐸𝐹 𝑑𝑜𝑙)] × 𝐶𝐶𝑂2 (Gypsum excluded)</t>
+  </si>
+  <si>
+    <t>Soil ameliorant type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Limestone</t>
+  </si>
+  <si>
+    <t>Dolomite</t>
+  </si>
+  <si>
+    <t>Gypsum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -234,12 +106,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
       <family val="2"/>
@@ -304,20 +170,20 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,33 +533,33 @@
         <v>0</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="17">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="17">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>2</v>
@@ -706,15 +572,15 @@
       <c r="B4">
         <v>0.3</v>
       </c>
-      <c r="C4">
-        <v>0</v>
+      <c r="C4" t="s">
+        <v>15</v>
       </c>
       <c r="I4">
-        <f>((A4*B4*$L$4*$L$6)+(A4*C4*$L$5*$L$7))*$L$9/1000</f>
-        <v>0.35639999999999999</v>
+        <f>IF(C4="Gypsum",0,((A4*B4*$L$4*$L$6)+(A4*(1-B4)*$L$5*$L$7))*$L$9/1000)</f>
+        <v>1.30735</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>0.9</v>
@@ -727,15 +593,15 @@
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5">
-        <v>0.5</v>
+      <c r="C5" t="s">
+        <v>16</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:I7" si="0">((A5*B5*$L$4*$L$6)+(A5*C5*$L$5*$L$7))*$L$9/1000</f>
-        <v>0.67925000000000002</v>
+        <f>IF(C5="Gypsum",0,((A5*B5*$L$4*$L$6)+(A5*(1-B5)*$L$5*$L$7))*$L$9/1000)</f>
+        <v>1.3585</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>0.95</v>
@@ -746,17 +612,17 @@
         <v>2000</v>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF(C6="Gypsum",0,((A6*B6*$L$4*$L$6)+(A6*(1-B6)*$L$5*$L$7))*$L$9/1000)</f>
+        <v>0.79200000000000004</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>0.12</v>
@@ -767,23 +633,36 @@
         <v>1000</v>
       </c>
       <c r="B7">
-        <v>0.3</v>
-      </c>
-      <c r="C7">
-        <v>0.4</v>
+        <v>0.6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>0.29993333333333333</v>
+        <f>IF(C7="Gypsum",0,((A7*B7*$L$4*$L$6)+(A7*(1-B7)*$L$5*$L$7))*$L$9/1000)</f>
+        <v>0.41873333333333329</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L7" s="2">
         <v>0.13</v>
       </c>
     </row>
     <row r="8" spans="1:12">
+      <c r="A8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8">
+        <f>IF(C8="Gypsum",0,((A8*B8*$L$4*$L$6)+(A8*(1-B8)*$L$5*$L$7))*$L$9/1000)</f>
+        <v>0</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
@@ -852,20 +731,20 @@
     </row>
     <row r="22" spans="2:12">
       <c r="G22" t="str">
-        <f t="shared" ref="G22:G25" si="1">IF(ISBLANK(C22), "", D22/C22)</f>
+        <f t="shared" ref="G22:G25" si="0">IF(ISBLANK(C22), "", D22/C22)</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="G23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="2:12">
       <c r="G24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K24" s="2"/>
@@ -873,7 +752,7 @@
     </row>
     <row r="25" spans="2:12">
       <c r="G25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K25" s="2"/>

--- a/packages/calculators/src/modules/test/5.3-lime.xlsx
+++ b/packages/calculators/src/modules/test/5.3-lime.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBC98C2-61D3-874A-BBFD-71C428AB48F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDDEEBB-D154-1F4A-9AEF-EF3FE7B9E989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="5.3.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -199,6 +197,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cco2" refersTo="='common'!$B$2"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>3.67</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -577,7 +597,7 @@
       </c>
       <c r="I4">
         <f>IF(C4="Gypsum",0,((A4*B4*$L$4*$L$6)+(A4*(1-B4)*$L$5*$L$7))*$L$9/1000)</f>
-        <v>1.30735</v>
+        <v>1.3085385</v>
       </c>
       <c r="K4" t="s">
         <v>8</v>
@@ -598,7 +618,7 @@
       </c>
       <c r="I5">
         <f>IF(C5="Gypsum",0,((A5*B5*$L$4*$L$6)+(A5*(1-B5)*$L$5*$L$7))*$L$9/1000)</f>
-        <v>1.3585</v>
+        <v>1.3597349999999999</v>
       </c>
       <c r="K5" t="s">
         <v>9</v>
@@ -619,7 +639,7 @@
       </c>
       <c r="I6">
         <f>IF(C6="Gypsum",0,((A6*B6*$L$4*$L$6)+(A6*(1-B6)*$L$5*$L$7))*$L$9/1000)</f>
-        <v>0.79200000000000004</v>
+        <v>0.79271999999999998</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -640,7 +660,7 @@
       </c>
       <c r="I7">
         <f>IF(C7="Gypsum",0,((A7*B7*$L$4*$L$6)+(A7*(1-B7)*$L$5*$L$7))*$L$9/1000)</f>
-        <v>0.41873333333333329</v>
+        <v>0.41911399999999999</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>11</v>
@@ -672,8 +692,8 @@
         <v>1</v>
       </c>
       <c r="L9" s="2">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
     </row>
     <row r="10" spans="1:12">
